--- a/frontend/public/resources/template/任务工时管理导入模板.xlsx
+++ b/frontend/public/resources/template/任务工时管理导入模板.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="任务工单管理" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="任务工时管理" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -472,60 +472,65 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>所属公司</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>所属TL</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>模块</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>任务描述</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>开始日期</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>结束日期</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>预计工时</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>责任人</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>完成状态</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>实际完成日期</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>实际工时</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>实际完成人</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>任务进度跟进描述</t>
         </is>
